--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/exercise-schema/createExerciseSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/exercise-schema/createExerciseSchema-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="174">
-  <si>
-    <t>Statement: createExerciseSchema – validate input for creating a new exercise.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="177">
+  <si>
+    <t>Statement: createExerciseSchema – Validates input for creating a new exercise using Zod safeParse. Returns { success: true, data } when all required fields are present and satisfy their constraints. Returns { success: false, error } with a path pointing to the offending field when any constraint is violated. name is required (8–64 characters after trimming, not whitespace-only; surrounding whitespace trimmed; empty string rejected). description is optional; when absent the field is undefined; when present it accepts an empty string, a whitespace-only string (trimmed to ""), or a non-empty string up to 1024 characters after trimming; surrounding whitespace trimmed. muscleGroup is required and must be a valid MuscleGroup enum value. equipmentNeeded is required and must be a valid Equipment enum value.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: CreateExerciseInput { name, description, muscleGroup, equipmentNeeded }</t>
+    <t>Input: CreateExerciseInput { name: string, description?: string, muscleGroup: MuscleGroup, equipmentNeeded: Equipment }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>Input values passed to Zod.safeParse()</t>
+    <t>Input is passed directly to createExerciseSchema.safeParse(). name: required, 8–64 characters after trim, not whitespace-only, empty string rejected. description: optional; when present, trimmed before length check, max 1024 characters after trim, whitespace-only trimmed to "". muscleGroup: required, must be a valid MuscleGroup enum member. equipmentNeeded: required, must be a valid Equipment enum member.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: { success: boolean, data?, error? }</t>
+    <t>Output: { success: boolean, data?: CreateExerciseInput, error?: ZodError }</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Validation results match constraints.</t>
+    <t>On success: parsed data contains the supplied fields with name and description trimmed. On failure: error.issues[0].path contains the name of the offending field.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -67,70 +67,76 @@
     <t>All fields valid</t>
   </si>
   <si>
-    <t>All constraints met</t>
-  </si>
-  <si>
-    <t>Description presence</t>
-  </si>
-  <si>
-    <t>Absent</t>
-  </si>
-  <si>
-    <t>Description value</t>
-  </si>
-  <si>
-    <t>Empty string ""</t>
-  </si>
-  <si>
-    <t>MuscleGroup</t>
-  </si>
-  <si>
-    <t>Valid enum</t>
-  </si>
-  <si>
-    <t>Invalid enum</t>
-  </si>
-  <si>
-    <t>EquipmentNeeded</t>
-  </si>
-  <si>
-    <t>Name presence</t>
-  </si>
-  <si>
-    <t>Present</t>
-  </si>
-  <si>
-    <t>Missing</t>
-  </si>
-  <si>
-    <t>Name value</t>
-  </si>
-  <si>
-    <t>Non-empty</t>
-  </si>
-  <si>
-    <t>Empty string</t>
-  </si>
-  <si>
-    <t>MuscleGroup presence</t>
-  </si>
-  <si>
-    <t>EquipmentNeeded presence</t>
-  </si>
-  <si>
-    <t>Name whitespace</t>
-  </si>
-  <si>
-    <t>Surrounding whitespace (trimmed)</t>
-  </si>
-  <si>
-    <t>Whitespace-only</t>
-  </si>
-  <si>
-    <t>Description whitespace</t>
-  </si>
-  <si>
-    <t>Whitespace-only → trimmed to ""</t>
+    <t>All required fields present with valid values, description present and valid → success: true, parsed data matches trimmed input</t>
+  </si>
+  <si>
+    <t>description presence</t>
+  </si>
+  <si>
+    <t>description field absent → success: true, parsed description is undefined</t>
+  </si>
+  <si>
+    <t>description value</t>
+  </si>
+  <si>
+    <t>description: "" (empty string) → success: true, parsed description is ""</t>
+  </si>
+  <si>
+    <t>muscleGroup value</t>
+  </si>
+  <si>
+    <t>muscleGroup: MuscleGroup.CHEST (valid enum member) → success: true</t>
+  </si>
+  <si>
+    <t>muscleGroup: "INVALID" (not a valid enum member) → success: false, error path contains "muscleGroup"</t>
+  </si>
+  <si>
+    <t>equipmentNeeded value</t>
+  </si>
+  <si>
+    <t>equipmentNeeded: Equipment.BARBELL (valid enum member) → success: true</t>
+  </si>
+  <si>
+    <t>equipmentNeeded: "INVALID" (not a valid enum member) → success: false, error path contains "equipmentNeeded"</t>
+  </si>
+  <si>
+    <t>name presence</t>
+  </si>
+  <si>
+    <t>name field absent → success: false, error path contains "name"</t>
+  </si>
+  <si>
+    <t>name value</t>
+  </si>
+  <si>
+    <t>name: "" (empty string) → success: false, error path contains "name"</t>
+  </si>
+  <si>
+    <t>muscleGroup presence</t>
+  </si>
+  <si>
+    <t>muscleGroup field absent → success: false, error path contains "muscleGroup"</t>
+  </si>
+  <si>
+    <t>equipmentNeeded presence</t>
+  </si>
+  <si>
+    <t>equipmentNeeded field absent → success: false, error path contains "equipmentNeeded"</t>
+  </si>
+  <si>
+    <t>name content</t>
+  </si>
+  <si>
+    <t>name: "  Bench Press  " (surrounding whitespace) → success: true, parsed name is "Bench Press"</t>
+  </si>
+  <si>
+    <t>name: "         " (whitespace-only) → success: false, error path contains "name"</t>
+  </si>
+  <si>
+    <t>description content</t>
+  </si>
+  <si>
+    <t>description: "  some description  " (surrounding whitespace) → success: true, parsed description is "some description"; description: "     " (whitespace-only) → success: true, parsed description is ""</t>
   </si>
   <si>
     <t>No TC</t>
@@ -151,10 +157,10 @@
     <t>EC-1</t>
   </si>
   <si>
-    <t>Valid all fields</t>
-  </si>
-  <si>
-    <t>success: true</t>
+    <t>all required fields provided with valid values: name "Bench Press", description "A chest exercise", muscleGroup MuscleGroup.CHEST, equipmentNeeded Equipment.BARBELL</t>
+  </si>
+  <si>
+    <t>success: true, parsed data matches trimmed input</t>
   </si>
   <si>
     <t>Passed</t>
@@ -163,70 +169,88 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>Description absent</t>
+    <t>valid exercise data with description field absent</t>
+  </si>
+  <si>
+    <t>success: true, parsed description is undefined</t>
   </si>
   <si>
     <t>EC-3</t>
   </si>
   <si>
-    <t>Description=""</t>
+    <t>valid exercise data with description: "" (empty string)</t>
+  </si>
+  <si>
+    <t>success: true, parsed description is ""</t>
   </si>
   <si>
     <t>EC-4</t>
   </si>
   <si>
-    <t>muscleGroup="INVALID"</t>
-  </si>
-  <si>
-    <t>success: false</t>
+    <t>valid exercise data with muscleGroup: "INVALID" (not a valid enum member)</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "muscleGroup"</t>
   </si>
   <si>
     <t>EC-5</t>
   </si>
   <si>
-    <t>equipmentNeeded="INVALID"</t>
+    <t>valid exercise data with equipmentNeeded: "INVALID" (not a valid enum member)</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "equipmentNeeded"</t>
   </si>
   <si>
     <t>EC-6</t>
   </si>
   <si>
-    <t>Missing name</t>
+    <t>exercise data with name field absent</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "name"</t>
   </si>
   <si>
     <t>EC-7</t>
   </si>
   <si>
-    <t>name=""</t>
+    <t>valid exercise data with name: "" (empty string)</t>
   </si>
   <si>
     <t>EC-8</t>
   </si>
   <si>
-    <t>Missing muscleGroup</t>
+    <t>exercise data with muscleGroup field absent</t>
   </si>
   <si>
     <t>EC-9</t>
   </si>
   <si>
-    <t>Missing equipmentNeeded</t>
+    <t>exercise data with equipmentNeeded field absent</t>
   </si>
   <si>
     <t>EC-10</t>
   </si>
   <si>
-    <t>name="         " (whitespace only)</t>
-  </si>
-  <si>
-    <t>name="  Bench Press  " (padded)</t>
+    <t>valid exercise data with name: "         " (whitespace-only)</t>
+  </si>
+  <si>
+    <t>valid exercise data with name: "  Bench Press  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>success: true, parsed name is "Bench Press"</t>
   </si>
   <si>
     <t>EC-11</t>
   </si>
   <si>
-    <t>description="     " (whitespace only)</t>
-  </si>
-  <si>
-    <t>description="  some description  " (padded)</t>
+    <t>valid exercise data with description: "     " (whitespace-only)</t>
+  </si>
+  <si>
+    <t>valid exercise data with description: "  some description  " (surrounding whitespace)</t>
+  </si>
+  <si>
+    <t>success: true, parsed description is "some description"</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -235,166 +259,196 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>Name length</t>
-  </si>
-  <si>
-    <t>7 chars (Below Min)</t>
-  </si>
-  <si>
-    <t>8 chars (At Min)</t>
-  </si>
-  <si>
-    <t>9 chars (Above Min)</t>
-  </si>
-  <si>
-    <t>63 chars (Below Max)</t>
-  </si>
-  <si>
-    <t>64 chars (At Max)</t>
-  </si>
-  <si>
-    <t>65 chars (Above Max)</t>
-  </si>
-  <si>
-    <t>8 whitespace chars (Whitespace At Min)</t>
-  </si>
-  <si>
-    <t>8 chars padded with whitespace (At Min after trim)</t>
-  </si>
-  <si>
-    <t>64 chars padded with whitespace (At Max after trim)</t>
-  </si>
-  <si>
-    <t>65 chars padded with whitespace (Above Max after trim)</t>
-  </si>
-  <si>
-    <t>Description length</t>
-  </si>
-  <si>
-    <t>0 chars (At Min)</t>
-  </si>
-  <si>
-    <t>1 char (Above Min)</t>
-  </si>
-  <si>
-    <t>1023 chars (Below Max)</t>
-  </si>
-  <si>
-    <t>1024 chars (At Max)</t>
-  </si>
-  <si>
-    <t>1025 chars (Above Max)</t>
-  </si>
-  <si>
-    <t>1024 chars padded with whitespace (At Max after trim)</t>
-  </si>
-  <si>
-    <t>1025 chars padded with whitespace (Above Max after trim)</t>
+    <t>name length</t>
+  </si>
+  <si>
+    <t>name: "A".repeat(7) (min - 1): below minimum → success: false</t>
+  </si>
+  <si>
+    <t>name: "A".repeat(8) (min): at minimum → success: true, parsed name is "A".repeat(8)</t>
+  </si>
+  <si>
+    <t>name: "A".repeat(9) (min + 1): above minimum → success: true, parsed name is "A".repeat(9)</t>
+  </si>
+  <si>
+    <t>name: "A".repeat(63) (max - 1): below maximum → success: true, parsed name is "A".repeat(63)</t>
+  </si>
+  <si>
+    <t>name: "A".repeat(64) (max): at maximum → success: true, parsed name is "A".repeat(64)</t>
+  </si>
+  <si>
+    <t>name: "A".repeat(65) (max + 1): above maximum → success: false</t>
+  </si>
+  <si>
+    <t>name whitespace + trim</t>
+  </si>
+  <si>
+    <t>name: " ".repeat(8) (8 whitespace chars, empty after trim) → success: false</t>
+  </si>
+  <si>
+    <t>name: " " + "A".repeat(8) + " " (8 real chars after trim, at minimum) → success: true, parsed name is "A".repeat(8)</t>
+  </si>
+  <si>
+    <t>name: " " + "A".repeat(64) + " " (64 real chars after trim, at maximum) → success: true, parsed name is "A".repeat(64)</t>
+  </si>
+  <si>
+    <t>name: " " + "A".repeat(65) + " " (65 real chars after trim, above maximum) → success: false</t>
+  </si>
+  <si>
+    <t>description length</t>
+  </si>
+  <si>
+    <t>description: "" (length 0, min): at minimum → success: true, parsed description is ""</t>
+  </si>
+  <si>
+    <t>description: "A" (length 1, min + 1): above minimum → success: true, parsed description is "A"</t>
+  </si>
+  <si>
+    <t>description: "A".repeat(1023) (max - 1): below maximum → success: true</t>
+  </si>
+  <si>
+    <t>description: "A".repeat(1024) (max): at maximum → success: true</t>
+  </si>
+  <si>
+    <t>description: "A".repeat(1025) (max + 1): above maximum → success: false</t>
+  </si>
+  <si>
+    <t>description whitespace + trim</t>
+  </si>
+  <si>
+    <t>description: " " + "A".repeat(1024) + " " (1024 real chars after trim, at maximum) → success: true, parsed description is "A".repeat(1024)</t>
+  </si>
+  <si>
+    <t>description: " " + "A".repeat(1025) + " " (1025 real chars after trim, above maximum) → success: false</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 Name 7ch</t>
-  </si>
-  <si>
-    <t>name len 7</t>
-  </si>
-  <si>
-    <t>BVA-1 Name 8ch</t>
-  </si>
-  <si>
-    <t>name len 8</t>
-  </si>
-  <si>
-    <t>BVA-1 Name 9ch</t>
-  </si>
-  <si>
-    <t>name len 9</t>
-  </si>
-  <si>
-    <t>BVA-1 Name 63ch</t>
-  </si>
-  <si>
-    <t>name len 63</t>
-  </si>
-  <si>
-    <t>BVA-1 Name 64ch</t>
-  </si>
-  <si>
-    <t>name len 64</t>
-  </si>
-  <si>
-    <t>BVA-1 Name 65ch</t>
-  </si>
-  <si>
-    <t>name len 65</t>
-  </si>
-  <si>
-    <t>BVA-1 Name whitespace 8ch</t>
-  </si>
-  <si>
-    <t>name=" ".repeat(8)</t>
-  </si>
-  <si>
-    <t>BVA-1 Name padded 8ch after trim</t>
-  </si>
-  <si>
-    <t>name=" "+"A".repeat(8)+" "</t>
-  </si>
-  <si>
-    <t>BVA-1 Name padded 64ch after trim</t>
-  </si>
-  <si>
-    <t>name=" "+"A".repeat(64)+" "</t>
-  </si>
-  <si>
-    <t>BVA-1 Name padded 65ch after trim</t>
-  </si>
-  <si>
-    <t>name=" "+"A".repeat(65)+" "</t>
-  </si>
-  <si>
-    <t>BVA-2 Desc 0ch</t>
-  </si>
-  <si>
-    <t>description len 0</t>
-  </si>
-  <si>
-    <t>BVA-2 Desc 1ch</t>
-  </si>
-  <si>
-    <t>description len 1</t>
-  </si>
-  <si>
-    <t>BVA-2 Desc 1023ch</t>
-  </si>
-  <si>
-    <t>description len 1023</t>
-  </si>
-  <si>
-    <t>BVA-2 Desc 1024ch</t>
-  </si>
-  <si>
-    <t>description len 1024</t>
-  </si>
-  <si>
-    <t>BVA-2 Desc 1025ch</t>
-  </si>
-  <si>
-    <t>description len 1025</t>
-  </si>
-  <si>
-    <t>BVA-2 Desc padded 1024ch after trim</t>
-  </si>
-  <si>
-    <t>description=" "+"A".repeat(1024)+" "</t>
-  </si>
-  <si>
-    <t>BVA-2 Desc padded 1025ch after trim</t>
-  </si>
-  <si>
-    <t>description=" "+"A".repeat(1025)+" "</t>
+    <t>BVA-1  (name=7)</t>
+  </si>
+  <si>
+    <t>valid exercise data with name: "A".repeat(7) (7 characters)</t>
+  </si>
+  <si>
+    <t>BVA-2  (name=8)</t>
+  </si>
+  <si>
+    <t>valid exercise data with name: "A".repeat(8) (8 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed name is "A".repeat(8)</t>
+  </si>
+  <si>
+    <t>BVA-3  (name=9)</t>
+  </si>
+  <si>
+    <t>valid exercise data with name: "A".repeat(9) (9 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed name is "A".repeat(9)</t>
+  </si>
+  <si>
+    <t>BVA-4  (name=63)</t>
+  </si>
+  <si>
+    <t>valid exercise data with name: "A".repeat(63) (63 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed name is "A".repeat(63)</t>
+  </si>
+  <si>
+    <t>BVA-5  (name=64)</t>
+  </si>
+  <si>
+    <t>valid exercise data with name: "A".repeat(64) (64 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed name is "A".repeat(64)</t>
+  </si>
+  <si>
+    <t>BVA-6  (name=65)</t>
+  </si>
+  <si>
+    <t>valid exercise data with name: "A".repeat(65) (65 characters)</t>
+  </si>
+  <si>
+    <t>BVA-7  (ws=8)</t>
+  </si>
+  <si>
+    <t>valid exercise data with name: " ".repeat(8) (8 whitespace characters, empty after trim)</t>
+  </si>
+  <si>
+    <t>BVA-8  (pad→8)</t>
+  </si>
+  <si>
+    <t>valid exercise data with name: " " + "A".repeat(8) + " " (8 real characters after trim)</t>
+  </si>
+  <si>
+    <t>BVA-9  (pad→64)</t>
+  </si>
+  <si>
+    <t>valid exercise data with name: " " + "A".repeat(64) + " " (64 real characters after trim)</t>
+  </si>
+  <si>
+    <t>BVA-10 (pad→65)</t>
+  </si>
+  <si>
+    <t>valid exercise data with name: " " + "A".repeat(65) + " " (65 real characters after trim)</t>
+  </si>
+  <si>
+    <t>BVA-11 (desc=0)</t>
+  </si>
+  <si>
+    <t>valid exercise data with description: "" (0 characters)</t>
+  </si>
+  <si>
+    <t>BVA-12 (desc=1)</t>
+  </si>
+  <si>
+    <t>valid exercise data with description: "A" (1 character)</t>
+  </si>
+  <si>
+    <t>success: true, parsed description is "A"</t>
+  </si>
+  <si>
+    <t>BVA-13 (desc=1023)</t>
+  </si>
+  <si>
+    <t>valid exercise data with description: "A".repeat(1023) (1023 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed description is "A".repeat(1023)</t>
+  </si>
+  <si>
+    <t>BVA-14 (desc=1024)</t>
+  </si>
+  <si>
+    <t>valid exercise data with description: "A".repeat(1024) (1024 characters)</t>
+  </si>
+  <si>
+    <t>success: true, parsed description is "A".repeat(1024)</t>
+  </si>
+  <si>
+    <t>BVA-15 (desc=1025)</t>
+  </si>
+  <si>
+    <t>valid exercise data with description: "A".repeat(1025) (1025 characters)</t>
+  </si>
+  <si>
+    <t>success: false, error path contains "description"</t>
+  </si>
+  <si>
+    <t>BVA-16 (pad→1024)</t>
+  </si>
+  <si>
+    <t>valid exercise data with description: " " + "A".repeat(1024) + " " (1024 real characters after trim)</t>
+  </si>
+  <si>
+    <t>BVA-17 (pad→1025)</t>
+  </si>
+  <si>
+    <t>valid exercise data with description: " " + "A".repeat(1025) + " " (1025 real characters after trim)</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -403,100 +457,55 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Valid exercise data</t>
-  </si>
-  <si>
-    <t>Description field absent</t>
-  </si>
-  <si>
-    <t>Description empty string</t>
-  </si>
-  <si>
-    <t>MuscleGroup invalid enum</t>
-  </si>
-  <si>
-    <t>Equipment invalid enum</t>
-  </si>
-  <si>
-    <t>Name field missing</t>
-  </si>
-  <si>
-    <t>Name empty string</t>
-  </si>
-  <si>
-    <t>MuscleGroup field missing</t>
-  </si>
-  <si>
-    <t>Equipment field missing</t>
-  </si>
-  <si>
-    <t>Name whitespace-only</t>
-  </si>
-  <si>
-    <t>Name with surrounding whitespace</t>
-  </si>
-  <si>
-    <t>Description whitespace-only</t>
-  </si>
-  <si>
-    <t>Description with surrounding whitespace</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>name len 7 (Below Min)</t>
-  </si>
-  <si>
-    <t>name len 8 (At Min)</t>
-  </si>
-  <si>
-    <t>name len 9 (Above Min)</t>
-  </si>
-  <si>
-    <t>name len 63 (Below Max)</t>
-  </si>
-  <si>
-    <t>name len 64 (At Max)</t>
-  </si>
-  <si>
-    <t>name len 65 (Above Max)</t>
-  </si>
-  <si>
-    <t>name whitespace 8ch</t>
-  </si>
-  <si>
-    <t>name padded → 8ch after trim (At Min)</t>
-  </si>
-  <si>
-    <t>name padded → 64ch after trim (At Max)</t>
-  </si>
-  <si>
-    <t>name padded → 65ch after trim (Above Max)</t>
-  </si>
-  <si>
     <t>BVA-2</t>
   </si>
   <si>
-    <t>description len 0 (Min)</t>
-  </si>
-  <si>
-    <t>description len 1 (Above Min)</t>
-  </si>
-  <si>
-    <t>description len 1023 (Below Max)</t>
-  </si>
-  <si>
-    <t>description len 1024 (Max)</t>
-  </si>
-  <si>
-    <t>description len 1025 (Above Max)</t>
-  </si>
-  <si>
-    <t>description padded → 1024ch after trim (At Max)</t>
-  </si>
-  <si>
-    <t>description padded → 1025ch after trim (Above Max)</t>
+    <t>BVA-3</t>
+  </si>
+  <si>
+    <t>BVA-4</t>
+  </si>
+  <si>
+    <t>BVA-5</t>
+  </si>
+  <si>
+    <t>BVA-6</t>
+  </si>
+  <si>
+    <t>BVA-7</t>
+  </si>
+  <si>
+    <t>BVA-8</t>
+  </si>
+  <si>
+    <t>BVA-9</t>
+  </si>
+  <si>
+    <t>BVA-10</t>
+  </si>
+  <si>
+    <t>BVA-11</t>
+  </si>
+  <si>
+    <t>BVA-12</t>
+  </si>
+  <si>
+    <t>BVA-13</t>
+  </si>
+  <si>
+    <t>BVA-14</t>
+  </si>
+  <si>
+    <t>BVA-15</t>
+  </si>
+  <si>
+    <t>BVA-16</t>
+  </si>
+  <si>
+    <t>BVA-17</t>
   </si>
   <si>
     <t>Testing</t>
@@ -529,7 +538,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>EXM-01</t>
+    <t>SCHEMA-07</t>
   </si>
   <si>
     <t>n/a</t>
@@ -1140,10 +1149,10 @@
         <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1151,13 +1160,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1165,10 +1174,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>30</v>
@@ -1182,10 +1191,10 @@
         <v>31</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1193,13 +1202,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1207,13 +1216,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1221,13 +1230,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1250,19 +1259,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1270,16 +1279,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1287,16 +1296,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1304,16 +1313,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1321,16 +1330,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1338,16 +1347,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1355,16 +1364,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1372,16 +1381,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1389,16 +1398,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1406,16 +1415,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1423,16 +1432,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1440,16 +1449,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1457,16 +1466,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1474,16 +1483,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1504,13 +1513,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1518,186 +1527,186 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+      <c r="A3" s="1">
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
+      <c r="A4" s="1">
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
+      <c r="A5" s="1">
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
+      <c r="A6" s="1">
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
+      <c r="A7" s="1">
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>1</v>
+      <c r="A8" s="1">
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
+      <c r="A9" s="1">
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>1</v>
+      <c r="A10" s="1">
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>1</v>
+      <c r="A11" s="1">
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>1</v>
+      <c r="A13" s="1">
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>1</v>
+      <c r="A14" s="1">
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>1</v>
+      <c r="A15" s="1">
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>1</v>
+      <c r="A16" s="1">
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>1</v>
+      <c r="A17" s="1">
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>1</v>
+      <c r="A18" s="1">
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1720,19 +1729,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1740,16 +1749,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1757,16 +1766,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1774,16 +1783,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1791,16 +1800,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1808,16 +1817,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1825,16 +1834,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1842,16 +1851,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1859,16 +1868,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="E9" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1876,16 +1885,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1893,16 +1902,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1910,16 +1919,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1927,16 +1936,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1944,16 +1953,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>45</v>
+        <v>133</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1961,16 +1970,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1978,16 +1987,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>53</v>
+        <v>139</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1995,16 +2004,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2012,16 +2021,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>53</v>
+        <v>139</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2045,22 +2054,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2068,19 +2077,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2088,19 +2097,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2108,19 +2117,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2128,19 +2137,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2148,19 +2157,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2168,19 +2177,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>133</v>
+        <v>62</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2188,19 +2197,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2208,19 +2217,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>135</v>
+        <v>67</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2228,19 +2237,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2248,19 +2257,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2268,19 +2277,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2288,19 +2297,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2308,19 +2317,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>140</v>
+        <v>76</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2331,16 +2340,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2351,16 +2360,16 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2371,16 +2380,16 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2391,16 +2400,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2411,16 +2420,16 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2431,16 +2440,16 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2451,16 +2460,16 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2471,16 +2480,16 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2491,16 +2500,16 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2511,16 +2520,16 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2531,16 +2540,16 @@
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2551,16 +2560,16 @@
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2571,16 +2580,16 @@
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>45</v>
+        <v>133</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2591,16 +2600,16 @@
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2611,16 +2620,16 @@
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>53</v>
+        <v>139</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2631,16 +2640,16 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2651,16 +2660,16 @@
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>53</v>
+        <v>139</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2688,16 +2697,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -2705,39 +2714,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>169</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B3" s="1">
         <v>30</v>
@@ -2752,19 +2761,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/exercise-schema/createExerciseSchema-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/exercise-schema/createExerciseSchema-bbt-form.xlsx
@@ -538,7 +538,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-07</t>
+    <t>SCHEMA-09</t>
   </si>
   <si>
     <t>n/a</t>
